--- a/templates/excel/treasury-runway.xlsx
+++ b/templates/excel/treasury-runway.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Obligations" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Runway_Calc" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Reserve_Discipline" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="README" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="_metadata" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet name="_metadata" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet name="README" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -772,13 +772,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D1000">
-    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
-      <formula>6</formula>
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND($A2&lt;&gt;"",D2&lt;6)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G1000">
-    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="0">
-      <formula>1</formula>
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>AND($A2&lt;&gt;"",G2&lt;1)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -889,129 +889,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># treasury-runway.xlsx (OPTIONAL)</t>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>spec_version</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1.0.0</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PURPOSE</t>
+          <t>generation_date</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Treasury reserve discipline. OPTIONAL in v1.0 — required only for organisations adopting the Unit Fund (Generation 2). Absent the Unit Fund, simpler treasury tracking via accountant + bank statements is sufficient.</t>
+          <t>oot_version</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1.0.0</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>DESIGN DECISION — monthly_burn_average is from historical Cash_Position deltas</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>NOT from future-committed Obligations. Burn is realised outflow over the rolling 3 months. R8 writes this on each run. Obligations forecasts forward; Cash_Position records what actually happened.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>WRITTEN BY</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>- Routine R8 (Treasury Runway Update, weekly Monday 08:00) — populates Cash_Position + Obligations + Runway_Calc.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>- Manual at Reserve_Discipline parameter changes (founder authority).</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>READ BY</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>- Skill Pack S10 (Finance &amp; Treasury).</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>- Skill Pack S5 (Reporting &amp; BR) — runway_months in KPI block.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>DO NOT</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>- Open the Unit Fund without ≥6-9 months of attribution-accuracy data + reserve_coverage_ratio ≥1.0.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>- Change Reserve_Discipline parameters without a Brain ADR.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>- Bypass treasury runway discipline once the Unit Fund is open.</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>file_id</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>X8</t>
         </is>
       </c>
     </row>
@@ -1026,66 +963,129 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="110" customWidth="1" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>value</t>
+          <t># treasury-runway.xlsx (OPTIONAL)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>spec_version</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1.0.0</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>generation_date</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
+          <t>PURPOSE</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>oot_version</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1.0.0</t>
+          <t>Treasury reserve discipline. OPTIONAL in v1.0 — required only for organisations adopting the Unit Fund (Generation 2). Absent the Unit Fund, simpler treasury tracking via accountant + bank statements is sufficient.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>file_id</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>X8</t>
+      <c r="A5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DESIGN DECISION — monthly_burn_average is from historical Cash_Position deltas</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NOT from future-committed Obligations. Burn is realised outflow over the rolling 3 months. R8 writes this on each run. Obligations forecasts forward; Cash_Position records what actually happened.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>WRITTEN BY</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>- Routine R8 (Treasury Runway Update, weekly Monday 08:00) — populates Cash_Position + Obligations + Runway_Calc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>- Manual at Reserve_Discipline parameter changes (founder authority).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>READ BY</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>- Skill Pack S10 (Finance &amp; Treasury).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>- Skill Pack S5 (Reporting &amp; BR) — runway_months in KPI block.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>DO NOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>- Open the Unit Fund without ≥6-9 months of attribution-accuracy data + reserve_coverage_ratio ≥1.0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>- Change Reserve_Discipline parameters without a Brain ADR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>- Bypass treasury runway discipline once the Unit Fund is open.</t>
         </is>
       </c>
     </row>
